--- a/data/trans_dic/IP1008-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1008-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen trastornos huesos, articulaciones o musculares</t>
+          <t>Menores que padecen trastornos huesos, articulaciones o musculares (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,0; 6,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,55</t>
+          <t>0,26; 2,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,56</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,86</t>
+          <t>0,0; 5,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,31; 2,62</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,27 +1008,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,63</t>
+          <t>0,29; 2,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1037,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,65</t>
+          <t>0,28; 1,62</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,6</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,3</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 3,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,39</t>
+          <t>0,28; 2,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,12</t>
+          <t>0,25; 2,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,14</t>
+          <t>0,0; 5,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 5,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,71</t>
+          <t>0,0; 5,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 3,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 3,46</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,93</t>
+          <t>0,1; 1,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,19</t>
+          <t>0,2; 1,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,7</t>
+          <t>0,41; 1,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,2</t>
+          <t>0,2; 1,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,02</t>
+          <t>0,18; 1,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,8</t>
+          <t>0,08; 0,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,8</t>
+          <t>0,2; 0,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,87</t>
+          <t>0,24; 0,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,99</t>
+          <t>0,31; 0,99</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen trastornos huesos, articulaciones o musculares (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2667</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6078</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>524; 5528</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1442</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1442</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2192</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5148</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5377</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3344</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5202</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>672; 5715</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3393</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3708</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3159</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4842</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3009</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>644; 6345</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3258</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2980</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4379</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4651</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1231; 7043</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1362</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3122</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4469</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5372</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4221</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4686</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>654; 5455</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>719; 6247</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5534</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1253</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3101</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3871</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3465</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3939</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4456</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2559</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3498</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>6235</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3421</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>5981</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>6765</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>8183</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>646; 6631</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1348; 7853</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2738; 11264</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1349; 7503</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1262; 7225</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>588; 5742</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2677; 11338</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>3324; 11686</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>4291; 13621</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1008-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1008-Clase-trans_dic.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,23</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,74</t>
+          <t>0,26; 2,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,55</t>
+          <t>0,0; 5,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,09</t>
+          <t>0,0; 4,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,62</t>
+          <t>0,31; 2,59</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 3,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,84</t>
+          <t>0,29; 2,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,62</t>
+          <t>0,28; 1,66</t>
         </is>
       </c>
     </row>
@@ -1118,27 +1118,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,32</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,35</t>
+          <t>0,0; 3,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,36</t>
+          <t>0,28; 2,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,16</t>
+          <t>0,24; 2,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,08</t>
+          <t>0,0; 5,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,23</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,11</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,08</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,46</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
     </row>
@@ -1343,42 +1343,42 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,17</t>
+          <t>0,19; 1,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,68</t>
+          <t>0,43; 1,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,1</t>
+          <t>0,2; 1,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,01</t>
+          <t>0,18; 1,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,81</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,86</t>
+          <t>0,19; 0,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,84</t>
+          <t>0,24; 0,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,99</t>
+          <t>0,32; 0,99</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2667</t>
+          <t>0; 2676</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 6078</t>
+          <t>0; 4757</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>524; 5528</t>
+          <t>527; 5322</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5148</t>
+          <t>0; 4973</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5377</t>
+          <t>0; 4555</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3344</t>
+          <t>0; 3359</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5202</t>
+          <t>0; 4529</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>672; 5715</t>
+          <t>677; 5667</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3393</t>
+          <t>0; 3326</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3708</t>
+          <t>0; 3228</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2128,17 +2128,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4842</t>
+          <t>0; 4226</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3009</t>
+          <t>0; 3492</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>644; 6345</t>
+          <t>637; 6620</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2148,27 +2148,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3258</t>
+          <t>0; 3242</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2980</t>
+          <t>0; 2800</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4379</t>
+          <t>0; 4334</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4651</t>
+          <t>0; 4675</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1231; 7043</t>
+          <t>1203; 7200</t>
         </is>
       </c>
     </row>
@@ -2291,27 +2291,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3122</t>
+          <t>0; 3285</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4469</t>
+          <t>0; 4980</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5372</t>
+          <t>0; 5170</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4221</t>
+          <t>0; 4786</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4686</t>
+          <t>0; 4697</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>654; 5455</t>
+          <t>654; 5428</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>719; 6247</t>
+          <t>683; 6759</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5534</t>
+          <t>0; 5689</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3101</t>
+          <t>0; 3098</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3871</t>
+          <t>0; 4415</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3465</t>
+          <t>0; 3223</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3939</t>
+          <t>0; 4559</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4456</t>
+          <t>0; 4345</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>646; 6631</t>
+          <t>653; 6626</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1348; 7853</t>
+          <t>1314; 7733</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2738; 11264</t>
+          <t>2860; 11181</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1349; 7503</t>
+          <t>1353; 8259</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1262; 7225</t>
+          <t>1255; 7319</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>588; 5742</t>
+          <t>0; 5207</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2677; 11338</t>
+          <t>2568; 10781</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3324; 11686</t>
+          <t>3392; 12661</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4291; 13621</t>
+          <t>4474; 13619</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1008-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1008-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,22 +625,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,5%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,88</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,64</t>
+          <t>0,26; 2,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -740,27 +740,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,56%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,31</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 4,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,59</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
     </row>
@@ -845,22 +845,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,15%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,96</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,33</t>
+          <t>0,28; 2,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,66</t>
+          <t>0,28; 1,65</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 3,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,36</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,35</t>
+          <t>0,28; 2,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,34</t>
+          <t>0,22; 2,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
     </row>
@@ -1180,27 +1180,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,07</t>
+          <t>0,0; 4,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,75</t>
+          <t>0,0; 6,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,37</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,04</t>
+          <t>0,2; 1,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,15</t>
+          <t>0,18; 1,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,67</t>
+          <t>0,08; 0,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,21</t>
+          <t>0,1; 0,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,03</t>
+          <t>0,2; 1,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,4; 1,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,81</t>
+          <t>0,2; 0,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,91</t>
+          <t>0,25; 0,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,99</t>
+          <t>0,3; 0,99</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,22 +1533,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1586,22 +1586,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>527</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2676</t>
+          <t>0; 4104</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4757</t>
+          <t>0; 2907</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>527; 5322</t>
+          <t>527; 5142</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1701,27 +1701,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1442</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1467</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4973</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4555</t>
+          <t>0; 3634</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5157</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3359</t>
+          <t>0; 5138</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4529</t>
+          <t>0; 4486</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>677; 5667</t>
+          <t>0; 5978</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4259</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3326</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3228</t>
+          <t>0; 3371</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1379</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>694</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2571</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4226</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3492</t>
+          <t>0; 3212</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>637; 6620</t>
+          <t>0; 2972</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4991</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3242</t>
+          <t>0; 3911</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2800</t>
+          <t>621; 5889</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4334</t>
+          <t>0; 4042</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4675</t>
+          <t>0; 4436</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1203; 7200</t>
+          <t>1224; 7161</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1362</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1579</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1390</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3285</t>
+          <t>0; 4204</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4980</t>
+          <t>0; 4103</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5170</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4786</t>
+          <t>0; 3263</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4697</t>
+          <t>0; 5368</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 6000</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>654; 5428</t>
+          <t>651; 5538</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>683; 6759</t>
+          <t>647; 6141</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5689</t>
+          <t>0; 5263</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2406,27 +2406,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>617</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1281</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4006</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3098</t>
+          <t>0; 3193</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4415</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3223</t>
+          <t>0; 3748</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4559</t>
+          <t>0; 4444</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4345</t>
+          <t>0; 3828</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3421</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>2559</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>3498</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>6235</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3421</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>3267</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>653; 6626</t>
+          <t>1363; 8190</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1314; 7733</t>
+          <t>1271; 7297</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2860; 11181</t>
+          <t>588; 5646</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1353; 8259</t>
+          <t>645; 5949</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1255; 7319</t>
+          <t>1324; 8005</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 5207</t>
+          <t>2661; 11400</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2568; 10781</t>
+          <t>2702; 10588</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3392; 12661</t>
+          <t>3437; 12088</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4474; 13619</t>
+          <t>4097; 13652</t>
         </is>
       </c>
     </row>
